--- a/docs/test-data/tire-import/01-valid-50.xlsx
+++ b/docs/test-data/tire-import/01-valid-50.xlsx
@@ -31,37 +31,19 @@
     <t>หมายเหตุ</t>
   </si>
   <si>
-    <t>GOODYEAR</t>
-  </si>
-  <si>
-    <t>KMAX S</t>
-  </si>
-  <si>
-    <t>295/80R22.5</t>
+    <t>CHENGSHAN</t>
+  </si>
+  <si>
+    <t>CST-35</t>
+  </si>
+  <si>
+    <t>11R22.5 16PR</t>
   </si>
   <si>
     <t>SEED1020-A0001</t>
   </si>
   <si>
-    <t>HANKOOK</t>
-  </si>
-  <si>
-    <t>AH35</t>
-  </si>
-  <si>
-    <t>315/80R22.5</t>
-  </si>
-  <si>
     <t>SEED1020-A0002</t>
-  </si>
-  <si>
-    <t>CHENGSHAN</t>
-  </si>
-  <si>
-    <t>CST-35</t>
-  </si>
-  <si>
-    <t>11R22.5 16PR</t>
   </si>
   <si>
     <t>SEED1020-A0003</t>
@@ -331,30 +313,30 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -368,35 +350,35 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
         <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -410,80 +392,80 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -497,38 +479,38 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
@@ -542,35 +524,35 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -584,38 +566,38 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -629,77 +611,77 @@
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
@@ -713,38 +695,38 @@
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E29" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
@@ -758,35 +740,35 @@
         <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35">
@@ -800,35 +782,35 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38">
@@ -842,80 +824,80 @@
         <v>7</v>
       </c>
       <c r="D38" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E41" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D42" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D43" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E43" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44">
@@ -929,35 +911,35 @@
         <v>7</v>
       </c>
       <c r="D44" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D45" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D46" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E46" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47">
@@ -971,35 +953,35 @@
         <v>7</v>
       </c>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50">
@@ -1013,24 +995,24 @@
         <v>7</v>
       </c>
       <c r="D50" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E50" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D51" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E51" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
